--- a/data/data_replicated/2p_nomod_sFRiman/traces_references.xlsx
+++ b/data/data_replicated/2p_nomod_sFRiman/traces_references.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t xml:space="preserve">trace</t>
   </si>
@@ -20,7 +20,7 @@
     <t xml:space="preserve">reference</t>
   </si>
   <si>
-    <t xml:space="preserve">c31-c32-31d2-32d3S30-45-00156-2278-2293.csv</t>
+    <t xml:space="preserve">c31-c32-31d3a-32d3a-00078-00078-3494-4326.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c31</t>
@@ -29,45 +29,18 @@
     <t xml:space="preserve">c32</t>
   </si>
   <si>
-    <t xml:space="preserve">c31-c32-31d2U60-32d3-025-30-13581-13667.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c31-c32-31d3-32d3-30-45-1252-1345.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c31-c32-31d3a-32d3a-00625-00625-29248-31167.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c31-c32-31d3a-32d3a-0125-0125-52403-64824.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c32-c31-32d3-31d3U15-45-00156-1345-1515.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c31-32d3-31d3U60-30-00313-1132-1201.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c31-32d3S30-31d3-00156-15-2293-2446.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c31-32d3U60-31d2-00313-45-4812-4882.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c32-c31-32d3a-31d3a-00156-00156-6213-6584.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c32-c31-32d3a-31d3a-003125-003125-10650-11425.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c32-c31-32d4I15-31d3S10-003125-011-14272-15824.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c31-32d4I22-31d4I35-00156-003125-7266-7632.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c32-c31-32d4I35-31d2S10-003125-00625-10351-10549.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c33-c34-33d2a-34d2a-0125-025-107564-194058.csv</t>
   </si>
   <si>
@@ -116,7 +89,7 @@
     <t xml:space="preserve">c33-c34-33d4c-34d4c-00078-003-2507-4392.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c35-c50-35d2-50d2c-15-05-9839-90741.csv</t>
+    <t xml:space="preserve">c35-c50-35d3a-50d2a-003125-025-12329-106577.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c35</t>
@@ -125,43 +98,28 @@
     <t xml:space="preserve">c50</t>
   </si>
   <si>
-    <t xml:space="preserve">c35-c50-35d2-50d2c-30-05-9957-90741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d2S30-50d2c-0125-05-12898-90741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d3-50d2c-30-05-11105-90741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d3-50d2d-30-05-7217-49389.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d3I22-50d2c-00625-05-17021-90741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d3S30-50d3c-003125-0125-2169-24073.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d3a-50d2a-003125-025-12329-106577.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c35-c50-35d3a-50d2a-00625-05-31784-164959.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c35-c50-35d3a-50d2c-003125-05-12329-90741.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c50-35d3a-50d2d-00078-0125-2745-25159.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c50-35d3a-50d2d-00078-025-2745-34331.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c50-35d3a-50d2d-00156-05-5558-49389.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c35-c50-35d3a-50d3c-00078-0125-2745-24073.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c35-c50-35d3a-50d4a-00156-016-5558-67760.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c35-c50-35d4I15-50d2d-00156-025-3410-34331.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d4I22-50d2d-00156-0125-3169-25159.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c35-c50-35d4I35-50d2c-00625-05-16125-90741.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d1-40d2S10-30-0125-11062-21763.csv</t>
+    <t xml:space="preserve">c39-c40-39d3a-40d3a-00078-00078-2522-3898.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c39</t>
@@ -170,30 +128,15 @@
     <t xml:space="preserve">c40</t>
   </si>
   <si>
-    <t xml:space="preserve">c39-c40-39d2-40d2-30-45-6363-12518.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d2-40d2S10-15-025-19843-41683.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d2-40d3-30-15-2498-4389.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d2-40d3-45-30-634-2172.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d3-40d3-15-15-4689-9311.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d3-40d4I35-15-00156-2976-6008.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d3S2-40d3-003125-15-8431-17934.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c39-c40-39d3a-40d3a-00078-00156-2522-6419.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c39-c40-39d3a-40d3a-00156-003125-6855-14282.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c39-c40-39d3a-40d3a-00156-00625-6855-19247.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c39-c40-39d3a-40d3a-003125-00625-11974-19247.csv</t>
   </si>
   <si>
@@ -203,57 +146,51 @@
     <t xml:space="preserve">c39-c40-39d3a-40d3a-00625-025-33341-90806.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c39-c40-39d4I35-40d4I15-00156-003125-4825-10189.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c39-c40-39d4I35-40d4I15-00625-00625-14580-27418.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d2-15-15-17934-76397.csv</t>
+    <t xml:space="preserve">c40-c39-40d3a-39d3a-00156-00156-6419-6855.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3S10-41d1S30-012-05-13019-53029.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c41</t>
   </si>
   <si>
-    <t xml:space="preserve">c40-c41-40d3-41d2U15-15-05-17934-58426.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3-15-15-2875-10815.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3-30-30-5710-21253.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3U105-30-0125-2172-6429.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3U105-30-025-2954-11468.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3U60-15-0125-2875-9420.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d3U60-30-05-5710-17466.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3-41d4I35-15-00625-9311-31447.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d3S10-41d1S30-012-05-13019-53029.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c40-c41-40d3S10-41d2S30-003125-025-4068-24669.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c40-c41-40d3S10-41d3S30-00078-003125-915-3611.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c40-c41-40d3S10-41d3U60-00156-0125-2220-9420.csv</t>
+    <t xml:space="preserve">c40-c41-40d3a-41d2U105-00156-05-6419-30947.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d2U15-003125-05-14282-58426.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d2U15-00625-05-19247-58426.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3U105-00078-0125-3898-6429.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3U60-00078-0125-3898-9420.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3U60-00078-05-3898-17466.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3U60-00156-05-6419-17466.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3a-00078-003125-3898-10975.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c40-c41-40d3a-41d3a-00078-00625-3898-23585.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c40-c41-40d3a-41d3a-00156-00625-6419-23585.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c40-c41-40d3a-41d3a-003125-0125-14282-56267.csv</t>
   </si>
   <si>
@@ -263,15 +200,6 @@
     <t xml:space="preserve">c40-c41-40d3a-41d3a-0125-025-43736-99488.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c40-c41-40d4I15-41d2U105-003125-05-10189-30947.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d4I15-41d4I15-00156-00625-7052-28568.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c40-c41-40d4I22-41d2U15-003125-05-11080-58426.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c40-c41-40d4I22-41d4I15-00156-00625-7004-28568.csv</t>
   </si>
   <si>
@@ -293,7 +221,7 @@
     <t xml:space="preserve">c40-c41-40d4I35-41d4I35-00156-003125-6008-12973.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-42d3-43d1-15-30-7201-71485.csv</t>
+    <t xml:space="preserve">c42-c43-42d3S2-43d1S10-003125-025-5791-55144.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c42</t>
@@ -302,21 +230,9 @@
     <t xml:space="preserve">c43</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-42d3-43d2S10-15-0125-2288-21611.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c42-c43-42d3-43d3U15-45-00625-763-7676.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c42-c43-42d3S2-43d1S10-003125-025-5791-55144.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c42-c43-42d3S2-43d1S10-00625-05-11483-96121.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-42d3S2-43d2-00156-30-3242-34003.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c42-c43-42d3S2-43d2S10-00156-0125-3242-21611.csv</t>
   </si>
   <si>
@@ -335,12 +251,6 @@
     <t xml:space="preserve">c42-c43-42d3U15-43d2U60-0125-05-6885-56138.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-42d3U15-43d3I15-0125-025-6885-58885.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c42-c43-42d3U60-43d2-00313-45-1130-10499.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c42-c43-42d3U60-43d2U15-0125-05-11770-105488.csv</t>
   </si>
   <si>
@@ -350,9 +260,18 @@
     <t xml:space="preserve">c42-c43-42d3a-43d2a-00625-05-22419-215886.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c42-c43-42d3a-43d3a-00078-00156-3084-5674.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c42-c43-42d3a-43d3a-00078-003125-3084-10202.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c42-c43-42d3a-43d3a-00078-00625-3084-31591.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c42-c43-42d3a-43d3a-00156-0125-5154-47750.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c42-c43-42d4I15-43d2I35-003125-05-9801-97032.csv</t>
   </si>
   <si>
@@ -371,13 +290,10 @@
     <t xml:space="preserve">c42-c43-42d4I22-43d4I22-00156-0125-4636-24649.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c42-c43-42d4I35-43d2-00156-15-5185-44726.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c42-c43-42d4I35-43d3I35-00156-025-5185-45522.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-44d3-45d3-30-15-1816-2216.csv</t>
+    <t xml:space="preserve">c44-c45-44d3S30-45d3S2-00156-00078-1458-1709.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c44</t>
@@ -386,9 +302,6 @@
     <t xml:space="preserve">c45</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-44d3S30-45d3S2-00156-00078-1458-1709.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c45-44d3S30-45d3S2-00625-00156-4868-5460.csv</t>
   </si>
   <si>
@@ -398,58 +311,31 @@
     <t xml:space="preserve">c44-c45-44d3a-45d3a-0125-0125-45891-50820.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-44d4I15-45d2S2-0125-00625-24016-25018.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c45-44d4I15-45d4I15-00625-00625-13023-13256.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-44d4I35-45d2S2-00625-003125-10225-10768.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c45-44d4I35-45d4I35-003125-003125-4859-4992.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c45-c44-45d2-44d4I15-30-003125-7010-7449.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c45-c44-45d2S2-44d3S30-003125-019-10768-13907.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c45-c44-45d3-44d3-15-30-3795-3959.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d3-44d3-30-15-8847-9435.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c45-c44-45d3S2-44d3S30-00078-003125-1709-2662.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c45-c44-45d3a-44d3a-00078-00078-3180-3347.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c45-c44-45d3a-44d3a-00156-00156-5175-5690.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c45-c44-45d3a-44d3a-00156-003125-5175-10346.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c45-c44-45d3a-44d3a-003125-00625-13722-23280.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c45-c44-45d4I15-44d3-00156-45-3102-3148.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d4I15-44d3-0125-30-25277-25994.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d4I22-44d3S30-00156-003125-2505-2662.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d4I22-44d4I22-003125-003125-5717-6170.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d4I22-44d4I22-0125-0125-20858-21087.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c45-c44-45d4I22-44d4I35-00156-00156-2505-2947.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c45-c44-45d4I22-44d4I35-00625-00625-10173-10225.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c45-c44-45d4I35-44d4I15-00625-00625-12047-13023.csv</t>
@@ -922,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -930,151 +816,151 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -1082,7 +968,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1090,7 +976,7 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -1098,7 +984,7 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1106,7 +992,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -1114,7 +1000,7 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1122,7 +1008,7 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -1130,7 +1016,7 @@
         <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -1138,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -1146,7 +1032,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
@@ -1154,583 +1040,583 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
         <v>26</v>
-      </c>
-      <c r="B42" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
         <v>27</v>
-      </c>
-      <c r="B45" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s">
         <v>46</v>
-      </c>
-      <c r="B79" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B87" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B93" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B95" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B104" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B106" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B109" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B113" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="114">
@@ -1738,7 +1624,7 @@
         <v>67</v>
       </c>
       <c r="B114" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115">
@@ -1746,7 +1632,7 @@
         <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="116">
@@ -1754,7 +1640,7 @@
         <v>68</v>
       </c>
       <c r="B116" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="117">
@@ -1762,7 +1648,7 @@
         <v>68</v>
       </c>
       <c r="B117" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="118">
@@ -1770,7 +1656,7 @@
         <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119">
@@ -1778,380 +1664,380 @@
         <v>69</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>72</v>
+      </c>
+      <c r="B120" t="s">
         <v>70</v>
-      </c>
-      <c r="B120" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>73</v>
+      </c>
+      <c r="B123" t="s">
         <v>71</v>
-      </c>
-      <c r="B123" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B124" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B125" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B126" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B127" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B128" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B129" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B130" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B132" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B134" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B135" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B136" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B137" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B139" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B140" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B141" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B142" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B143" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B144" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B145" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B146" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B147" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B148" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B149" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B150" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B151" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B152" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B153" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B154" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B155" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B156" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B157" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B158" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B159" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B160" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B161" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B162" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B163" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B164" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B165" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B166" t="s">
         <v>94</v>
@@ -2159,7 +2045,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B167" t="s">
         <v>95</v>
@@ -2167,7 +2053,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B168" t="s">
         <v>94</v>
@@ -2175,7 +2061,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B169" t="s">
         <v>95</v>
@@ -2183,7 +2069,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B170" t="s">
         <v>94</v>
@@ -2191,7 +2077,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B171" t="s">
         <v>95</v>
@@ -2199,7 +2085,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B172" t="s">
         <v>94</v>
@@ -2207,7 +2093,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B173" t="s">
         <v>95</v>
@@ -2215,7 +2101,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B174" t="s">
         <v>94</v>
@@ -2223,7 +2109,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B175" t="s">
         <v>95</v>
@@ -2231,7 +2117,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B176" t="s">
         <v>94</v>
@@ -2239,7 +2125,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B177" t="s">
         <v>95</v>
@@ -2247,7 +2133,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B178" t="s">
         <v>94</v>
@@ -2255,7 +2141,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B179" t="s">
         <v>95</v>
@@ -2263,7 +2149,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B180" t="s">
         <v>94</v>
@@ -2271,7 +2157,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B181" t="s">
         <v>95</v>
@@ -2279,7 +2165,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B182" t="s">
         <v>94</v>
@@ -2287,7 +2173,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B183" t="s">
         <v>95</v>
@@ -2295,7 +2181,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B184" t="s">
         <v>94</v>
@@ -2303,7 +2189,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B185" t="s">
         <v>95</v>
@@ -2311,7 +2197,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B186" t="s">
         <v>94</v>
@@ -2319,7 +2205,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B187" t="s">
         <v>95</v>
@@ -2327,7 +2213,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B188" t="s">
         <v>94</v>
@@ -2335,7 +2221,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B189" t="s">
         <v>95</v>
@@ -2343,834 +2229,226 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B190" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B191" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B192" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B193" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B194" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B195" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>114</v>
+      </c>
+      <c r="B196" t="s">
         <v>110</v>
-      </c>
-      <c r="B196" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B197" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B198" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>115</v>
+      </c>
+      <c r="B199" t="s">
         <v>111</v>
-      </c>
-      <c r="B199" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B200" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B201" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B202" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B203" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B204" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B205" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B206" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B207" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B208" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B209" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B210" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B211" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B212" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B213" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B214" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B215" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B216" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B217" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>121</v>
-      </c>
-      <c r="B218" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>121</v>
-      </c>
-      <c r="B219" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>124</v>
-      </c>
-      <c r="B220" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>124</v>
-      </c>
-      <c r="B221" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>125</v>
-      </c>
-      <c r="B222" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>125</v>
-      </c>
-      <c r="B223" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>126</v>
-      </c>
-      <c r="B224" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>126</v>
-      </c>
-      <c r="B225" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>127</v>
-      </c>
-      <c r="B226" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>127</v>
-      </c>
-      <c r="B227" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>128</v>
-      </c>
-      <c r="B228" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>128</v>
-      </c>
-      <c r="B229" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>129</v>
-      </c>
-      <c r="B230" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>129</v>
-      </c>
-      <c r="B231" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>130</v>
-      </c>
-      <c r="B232" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>130</v>
-      </c>
-      <c r="B233" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>131</v>
-      </c>
-      <c r="B234" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>131</v>
-      </c>
-      <c r="B235" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>132</v>
-      </c>
-      <c r="B236" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>132</v>
-      </c>
-      <c r="B237" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>133</v>
-      </c>
-      <c r="B238" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>133</v>
-      </c>
-      <c r="B239" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>134</v>
-      </c>
-      <c r="B240" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>134</v>
-      </c>
-      <c r="B241" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>135</v>
-      </c>
-      <c r="B242" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>135</v>
-      </c>
-      <c r="B243" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>136</v>
-      </c>
-      <c r="B244" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>136</v>
-      </c>
-      <c r="B245" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>137</v>
-      </c>
-      <c r="B246" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>137</v>
-      </c>
-      <c r="B247" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>138</v>
-      </c>
-      <c r="B248" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>138</v>
-      </c>
-      <c r="B249" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>139</v>
-      </c>
-      <c r="B250" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>139</v>
-      </c>
-      <c r="B251" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>140</v>
-      </c>
-      <c r="B252" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>140</v>
-      </c>
-      <c r="B253" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>141</v>
-      </c>
-      <c r="B254" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>141</v>
-      </c>
-      <c r="B255" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>142</v>
-      </c>
-      <c r="B256" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>142</v>
-      </c>
-      <c r="B257" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>143</v>
-      </c>
-      <c r="B258" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>143</v>
-      </c>
-      <c r="B259" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>144</v>
-      </c>
-      <c r="B260" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>144</v>
-      </c>
-      <c r="B261" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>145</v>
-      </c>
-      <c r="B262" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>145</v>
-      </c>
-      <c r="B263" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>146</v>
-      </c>
-      <c r="B264" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>146</v>
-      </c>
-      <c r="B265" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>147</v>
-      </c>
-      <c r="B266" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="s">
-        <v>147</v>
-      </c>
-      <c r="B267" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="s">
-        <v>150</v>
-      </c>
-      <c r="B268" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="s">
-        <v>150</v>
-      </c>
-      <c r="B269" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="s">
-        <v>151</v>
-      </c>
-      <c r="B270" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s">
-        <v>151</v>
-      </c>
-      <c r="B271" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="s">
-        <v>152</v>
-      </c>
-      <c r="B272" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="s">
-        <v>152</v>
-      </c>
-      <c r="B273" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="s">
-        <v>153</v>
-      </c>
-      <c r="B274" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="s">
-        <v>153</v>
-      </c>
-      <c r="B275" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="s">
-        <v>154</v>
-      </c>
-      <c r="B276" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="s">
-        <v>154</v>
-      </c>
-      <c r="B277" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s">
-        <v>155</v>
-      </c>
-      <c r="B278" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="s">
-        <v>155</v>
-      </c>
-      <c r="B279" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>156</v>
-      </c>
-      <c r="B280" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s">
-        <v>156</v>
-      </c>
-      <c r="B281" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s">
-        <v>157</v>
-      </c>
-      <c r="B282" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s">
-        <v>157</v>
-      </c>
-      <c r="B283" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s">
-        <v>158</v>
-      </c>
-      <c r="B284" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="s">
-        <v>158</v>
-      </c>
-      <c r="B285" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="s">
-        <v>159</v>
-      </c>
-      <c r="B286" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="s">
-        <v>159</v>
-      </c>
-      <c r="B287" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="s">
-        <v>160</v>
-      </c>
-      <c r="B288" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="s">
-        <v>160</v>
-      </c>
-      <c r="B289" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="s">
-        <v>161</v>
-      </c>
-      <c r="B290" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="s">
-        <v>161</v>
-      </c>
-      <c r="B291" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="s">
-        <v>162</v>
-      </c>
-      <c r="B292" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s">
-        <v>162</v>
-      </c>
-      <c r="B293" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
